--- a/data/trans_bre/P1803_2016_2023-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1803_2016_2023-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,32</t>
+          <t>-1,72; 2,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,34</t>
+          <t>0,55; 4,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 87,01</t>
+          <t>-33,32; 82,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 141,58</t>
+          <t>5,77; 156,1</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-9,47</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-52,87%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,41</t>
+          <t>-0,24; 2,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 1,06</t>
+          <t>0,09; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 66,23</t>
+          <t>-5,67; 63,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-80,36; 13,28</t>
+          <t>0,91; 49,92</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 5,08</t>
+          <t>-1,5; 5,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,88</t>
+          <t>-0,89; 6,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 95,26</t>
+          <t>-16,21; 101,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 63,86</t>
+          <t>-6,44; 63,57</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-5,47</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-36,69%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,02</t>
+          <t>-0,09; 2,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 1,49</t>
+          <t>0,51; 3,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 51,96</t>
+          <t>-2,15; 51,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-75,23; 17,92</t>
+          <t>5,56; 44,31</t>
         </is>
       </c>
     </row>
